--- a/experiment_stimuli/Block2.xlsx
+++ b/experiment_stimuli/Block2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Frances\Desktop\sdt\experiment_stimuli\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Frances\Desktop\lab\sdtWhole\experiment_stimuli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5664903-B276-4421-8864-4E4A8D2EB0C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA71EF3-F744-499C-986A-F2513113A10D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8760" yWindow="1872" windowWidth="17172" windowHeight="11064" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="66600" yWindow="990" windowWidth="17280" windowHeight="8910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -67,12 +67,6 @@
     <t>The clever horse was a chorus.</t>
   </si>
   <si>
-    <t>The submarine's weapon was a sloth.</t>
-  </si>
-  <si>
-    <t>The yellow pen was a bullet.</t>
-  </si>
-  <si>
     <t>Metaphors</t>
   </si>
   <si>
@@ -95,6 +89,12 @@
   </si>
   <si>
     <t>The lumberjack tool was a chainsaw.</t>
+  </si>
+  <si>
+    <t>The submarine's weapon was a giraffe.</t>
+  </si>
+  <si>
+    <t>The oak tree was a bullet.</t>
   </si>
 </sst>
 </file>
@@ -380,7 +380,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -391,7 +391,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>5</v>
@@ -408,7 +408,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>5</v>
@@ -561,7 +561,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -578,7 +578,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -592,10 +592,10 @@
         <v>2</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>5</v>
@@ -609,10 +609,10 @@
         <v>2</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>5</v>
@@ -626,10 +626,10 @@
         <v>2</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>5</v>
@@ -643,10 +643,10 @@
         <v>2</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>5</v>

--- a/experiment_stimuli/Block2.xlsx
+++ b/experiment_stimuli/Block2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Frances\Desktop\lab\sdtWhole\experiment_stimuli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA71EF3-F744-499C-986A-F2513113A10D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30871DD1-84EF-4C0E-B0EE-40DC1D499A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="66600" yWindow="990" windowWidth="17280" windowHeight="8910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -91,10 +91,10 @@
     <t>The lumberjack tool was a chainsaw.</t>
   </si>
   <si>
-    <t>The submarine's weapon was a giraffe.</t>
-  </si>
-  <si>
     <t>The oak tree was a bullet.</t>
+  </si>
+  <si>
+    <t>The submarine weapon was a giraffe.</t>
   </si>
 </sst>
 </file>
@@ -561,7 +561,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -578,7 +578,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
